--- a/根管填充物像素長度_已配對_冠寬比例尺.xlsx
+++ b/根管填充物像素長度_已配對_冠寬比例尺.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,20 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>年齡</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>冠寬_原圖px</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>長寬比</t>
         </is>
@@ -524,9 +534,17 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>94.04730000000001</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>3.266873158506411</v>
       </c>
     </row>
@@ -570,9 +588,17 @@
         </is>
       </c>
       <c r="M3" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>85.33329999999999</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>2.371454051349239</v>
       </c>
     </row>
@@ -612,9 +638,17 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>85.33329999999999</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>2.889551909981215</v>
       </c>
     </row>
@@ -658,9 +692,17 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
+        <v>74</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>54.9333</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>3.571431171984934</v>
       </c>
     </row>
@@ -700,9 +742,17 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
+        <v>12</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>72.2666</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>2.955749959178929</v>
       </c>
     </row>
@@ -742,9 +792,17 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
+        <v>12</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>85.33329999999999</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>2.910241371188036</v>
       </c>
     </row>
@@ -788,9 +846,17 @@
         </is>
       </c>
       <c r="M8" t="n">
+        <v>20</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>73.06659999999999</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>3.476504996811129</v>
       </c>
     </row>
@@ -830,9 +896,17 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
+        <v>64</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>91.5444</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>3.217680163942306</v>
       </c>
     </row>
@@ -872,9 +946,17 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
+        <v>48</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>33.8667</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>3.199496850888926</v>
       </c>
     </row>
@@ -918,9 +1000,17 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
+        <v>30</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>71.5432</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>3.205589070659406</v>
       </c>
     </row>
@@ -960,9 +1050,17 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
+        <v>47</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>83.7333</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>2.946636523342565</v>
       </c>
     </row>
@@ -1006,9 +1104,17 @@
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
+        <v>47</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>72.5333</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>2.993678765477374</v>
       </c>
     </row>
@@ -1048,9 +1154,17 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
+        <v>60</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>3.101752717391304</v>
       </c>
     </row>
@@ -1090,9 +1204,17 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
+        <v>70</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>49.6</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>3.970618951612903</v>
       </c>
     </row>
@@ -1132,9 +1254,17 @@
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
+        <v>18</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>46.4</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>4.494056034482758</v>
       </c>
     </row>
@@ -1174,9 +1304,17 @@
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
+        <v>49</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>22.6667</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>4.136764504758082</v>
       </c>
     </row>
@@ -1216,9 +1354,17 @@
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
+        <v>47</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
         <v>41.0667</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>2.990926955416433</v>
       </c>
     </row>
@@ -1258,9 +1404,17 @@
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
+        <v>47</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
         <v>68.8</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>3.270542151162791</v>
       </c>
     </row>
@@ -1304,9 +1458,17 @@
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
+        <v>14</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>78.9333</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>3.25857527811456</v>
       </c>
     </row>
@@ -1350,9 +1512,17 @@
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
+        <v>36</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
         <v>106.5312</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>2.511132888768736</v>
       </c>
     </row>
@@ -1392,9 +1562,17 @@
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
+        <v>58</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
         <v>68.8</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>3.001643895348837</v>
       </c>
     </row>
@@ -1438,9 +1616,17 @@
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
+        <v>22</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
         <v>78.9333</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>2.840766824648152</v>
       </c>
     </row>
@@ -1484,9 +1670,17 @@
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
+        <v>28</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
         <v>85.86660000000001</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>2.312922603200779</v>
       </c>
     </row>
@@ -1530,9 +1724,17 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
+        <v>28</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
         <v>72.5333</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>2.698665302695452</v>
       </c>
     </row>
@@ -1576,9 +1778,17 @@
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
+        <v>32</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
         <v>37.3333</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>5.397867319524392</v>
       </c>
     </row>
@@ -1622,9 +1832,17 @@
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
+        <v>34</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
         <v>86.9333</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>2.648487978714716</v>
       </c>
     </row>
@@ -1668,9 +1886,17 @@
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
+        <v>41</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
         <v>70.9333</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>2.974370288707842</v>
       </c>
     </row>
@@ -1714,9 +1940,17 @@
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
+        <v>41</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
         <v>80.5333</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>2.850150186320441</v>
       </c>
     </row>
@@ -1756,9 +1990,17 @@
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
+        <v>52</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
         <v>97.9105</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>2.730636652861542</v>
       </c>
     </row>
@@ -1798,9 +2040,17 @@
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
+        <v>44</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
         <v>82.13330000000001</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>2.822554311101587</v>
       </c>
     </row>
@@ -1844,9 +2094,17 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
+        <v>25</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
         <v>40.0001</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>2.88000029999925</v>
       </c>
     </row>
@@ -1890,9 +2148,17 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
+        <v>25</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
         <v>38.6667</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>2.945617288260959</v>
       </c>
     </row>
@@ -1936,9 +2202,17 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
+        <v>59</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
         <v>30.9334</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>3.689743125553609</v>
       </c>
     </row>
@@ -1982,9 +2256,17 @@
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
+        <v>59</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
         <v>57.6</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>3.489177083333333</v>
       </c>
     </row>
@@ -2024,9 +2306,17 @@
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
+        <v>34</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
         <v>78.9333</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>2.665649352047868</v>
       </c>
     </row>
@@ -2066,9 +2356,17 @@
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
+        <v>34</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
         <v>64.5333</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>3.043865725137255</v>
       </c>
     </row>
@@ -2112,9 +2410,17 @@
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
+        <v>36</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
         <v>81.59990000000001</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>3.018166688929766</v>
       </c>
     </row>
@@ -2158,9 +2464,17 @@
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
+        <v>40</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
         <v>85.86660000000001</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>2.327353126826962</v>
       </c>
     </row>
@@ -2204,9 +2518,17 @@
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
+        <v>67</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
         <v>80.5333</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>2.890368332106098</v>
       </c>
     </row>
@@ -2250,9 +2572,17 @@
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
+        <v>67</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
         <v>43.7784</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>3.712780732050509</v>
       </c>
     </row>
@@ -2292,9 +2622,17 @@
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
+        <v>53</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
         <v>72.5333</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>3.102696278812628</v>
       </c>
     </row>
@@ -2338,9 +2676,17 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
+        <v>27</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
         <v>68.94799999999999</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>3.834823345129663</v>
       </c>
     </row>
@@ -2384,9 +2730,17 @@
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
+        <v>71</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
         <v>54.9333</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>3.57959925946557</v>
       </c>
     </row>
@@ -2426,9 +2780,17 @@
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
+        <v>55</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
         <v>52.2666</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>4.224296204459445</v>
       </c>
     </row>
@@ -2472,9 +2834,17 @@
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
+        <v>31</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
         <v>87.4666</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>2.312537585775599</v>
       </c>
     </row>
@@ -2518,9 +2888,17 @@
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
+        <v>32</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
         <v>45.8667</v>
       </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
         <v>2.663782221088502</v>
       </c>
     </row>
@@ -2564,9 +2942,17 @@
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
+        <v>32</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
         <v>45.8667</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>2.46535067925096</v>
       </c>
     </row>
@@ -2606,9 +2992,17 @@
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
+        <v>32</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
         <v>34.4</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>3.425476744186047</v>
       </c>
     </row>
@@ -2652,9 +3046,17 @@
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
+        <v>42</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
         <v>41.3334</v>
       </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
         <v>2.713713364978444</v>
       </c>
     </row>
@@ -2694,9 +3096,17 @@
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
+        <v>42</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
         <v>40.5334</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>2.809653273596589</v>
       </c>
     </row>
@@ -2740,9 +3150,17 @@
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
+        <v>42</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
         <v>30.9334</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>3.416478628278818</v>
       </c>
     </row>
@@ -2782,9 +3200,17 @@
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
+        <v>42</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
         <v>26.9334</v>
       </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
         <v>3.596920552176851</v>
       </c>
     </row>
@@ -2828,9 +3254,17 @@
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
+        <v>42</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
         <v>26.9334</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>3.687065131026904</v>
       </c>
     </row>
@@ -2878,9 +3312,17 @@
         </is>
       </c>
       <c r="M55" t="n">
+        <v>42</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
         <v>32.2667</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>2.93997526862059</v>
       </c>
     </row>

--- a/根管填充物像素長度_已配對_冠寬比例尺.xlsx
+++ b/根管填充物像素長度_已配對_冠寬比例尺.xlsx
@@ -3925,7 +3925,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>067_d0_jpg.rf.d69e1bebfb7e4f8d986ef8037968ad4d.jpg</t>
+          <t>067_d0_jpg.rf.ac90bce7f88c1b868e5f95777451272a.jpg</t>
         </is>
       </c>
       <c r="B64" t="n">

--- a/根管填充物像素長度_已配對_冠寬比例尺.xlsx
+++ b/根管填充物像素長度_已配對_冠寬比例尺.xlsx
@@ -501,14 +501,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>001_d1_jpg.rf.55ca288714ec60e15df18c82ae76bc67.jpg</t>
+          <t>001_d1_jpg.rf.55c174a77b98ec1352828ebfa5b9ab51.jpg</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>20.8458</v>
+        <v>20.9522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -546,23 +546,23 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>153.4844</v>
+        <v>125.2109</v>
       </c>
       <c r="P2" t="n">
-        <v>3.207051009744313</v>
+        <v>3.223417450078228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>002_d0_jpg.rf.b8790bc4063f3067d227a4e526ae4d5a.jpg</t>
+          <t>002_d0_jpg.rf.239b012acf3a5d81cc23f63768811eab.jpg</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>20.0144</v>
+        <v>19.8149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -608,23 +608,23 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>305.35</v>
+        <v>259.7937</v>
       </c>
       <c r="P3" t="n">
-        <v>2.354629769117406</v>
+        <v>2.331168538728999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>003_d1_jpg.rf.3973562f637d9898e830f77b6c80ee47.jpg</t>
+          <t>003_d1_jpg.rf.38cc6ea2963bec79f589d69fb3c38567.jpg</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>23.5</v>
       </c>
       <c r="C4" t="n">
-        <v>25.3772</v>
+        <v>26.8378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -662,23 +662,23 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>306.6375</v>
+        <v>245.0094</v>
       </c>
       <c r="P4" t="n">
-        <v>2.985557865557866</v>
+        <v>3.157393553063678</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>004_d3_jpg.rf.436425ea8d3cfea07d5ef2c70caae4b5.jpg</t>
+          <t>004_d3_jpg.rf.0908e2acaf0d93383f9ba4d0804e8011.jpg</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>17.7899</v>
+        <v>17.9625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -720,23 +720,23 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>196.8656</v>
+        <v>161.2875</v>
       </c>
       <c r="P5" t="n">
-        <v>3.557979149226681</v>
+        <v>3.592499728745253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>005_d1_jpg.rf.1d35baa3c5801a31e87ca0a899761d4b.jpg</t>
+          <t>005_d1_jpg.rf.93c30592402d913f3267450c16f2d887.jpg</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>21.5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.5166</v>
+        <v>19.2214</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -774,23 +774,23 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>261.25</v>
+        <v>213.75</v>
       </c>
       <c r="P6" t="n">
-        <v>3.002551578947369</v>
+        <v>2.957133567251462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>006_d1_jpg.rf.fb89dd26c09868f7f2e2c25b37391b5f.jpg</t>
+          <t>006_d1_jpg.rf.3c7d07d05aae59d1f393853f31eb78a9.jpg</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>22.6185</v>
+        <v>23.9883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>317.8922</v>
+        <v>255.475</v>
       </c>
       <c r="P7" t="n">
-        <v>2.660994827806407</v>
+        <v>2.822154026812799</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>007_d1_jpg.rf.2110ece5cbfd523ce6fcb59e5d6ad175.jpg</t>
+          <t>007_d1_jpg.rf.dd647087a302f451c265723a4c79a4f4.jpg</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>29.9955</v>
+        <v>29.8309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -868,7 +868,11 @@
       <c r="I8" t="n">
         <v>960</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
       <c r="K8" t="n">
         <v>11</v>
       </c>
@@ -886,23 +890,23 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="P8" t="n">
-        <v>3.528878544061302</v>
+        <v>3.509513425925926</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>008_d1_jpg.rf.1cb684b004a4e0ce882049570d799742.jpg</t>
+          <t>008_d1_jpg.rf.fbef341d23507d0e4aca06499a411bb3.jpg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>20.5</v>
       </c>
       <c r="C9" t="n">
-        <v>21.11</v>
+        <v>21.3665</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -940,23 +944,23 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>142.5078</v>
+        <v>121.7094</v>
       </c>
       <c r="P9" t="n">
-        <v>3.247698722455894</v>
+        <v>3.287156127628597</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>009_d1_jpg.rf.d07b2087243858aeb80be1e1ba7bb714.jpg</t>
+          <t>009_d1_jpg.rf.a4e9643443ee2e940ab17d8bc2f79ed4.jpg</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>19.934</v>
+        <v>19.9328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -994,23 +998,23 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>508.6125</v>
+        <v>418.7063</v>
       </c>
       <c r="P10" t="n">
-        <v>3.066776573521099</v>
+        <v>3.066582231984568</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>010_d1_jpg.rf.12ed75eb6a538870bf7c1892befd47be.jpg</t>
+          <t>010_d1_jpg.rf.9c2ea6a8287eca71401d1cb4a5b4c75c.jpg</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>16.1166</v>
+        <v>15.9975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1052,23 +1056,23 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>118.5875</v>
+        <v>99.375</v>
       </c>
       <c r="P11" t="n">
-        <v>3.223313587013808</v>
+        <v>3.199499874213837</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>011_d0_jpg.rf.24a3e73fb488d0e0a7ca2d4611dd2557.jpg</t>
+          <t>011_d0_jpg.rf.8592f84486d3e21026a0de8bd8475f37.jpg</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>23.8512</v>
+        <v>24.9094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1106,23 +1110,23 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>309.8531</v>
+        <v>255.9656</v>
       </c>
       <c r="P12" t="n">
-        <v>2.806025823204609</v>
+        <v>2.930517616429708</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012_d1_jpg.rf.6c455947b4199ab5255c85a091b58a31.jpg</t>
+          <t>012_d1_jpg.rf.8f5edc0c4d896e0ac72c42fad4b4ae7e.jpg</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>22.5</v>
       </c>
       <c r="C13" t="n">
-        <v>19.6822</v>
+        <v>19.9926</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1160,23 +1164,23 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>263.9875</v>
+        <v>219.5406</v>
       </c>
       <c r="P13" t="n">
-        <v>3.028023296557602</v>
+        <v>3.075790992645552</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>013_d1_jpg.rf.34ce0b922f6a8d44280cc06be70b40ad.jpg</t>
+          <t>013_d1_jpg.rf.b7990f89d66aa887a430c51d7385ddcd.jpg</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>20.5</v>
       </c>
       <c r="C14" t="n">
-        <v>26.3512</v>
+        <v>25.9433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1214,23 +1218,23 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>263.2641</v>
+        <v>220.9781</v>
       </c>
       <c r="P14" t="n">
-        <v>3.100146582842096</v>
+        <v>3.052157204718476</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>014_d2_jpg.rf.dde521f03ce3dfcd7df92ba1e3713e58.jpg</t>
+          <t>014_d2_jpg.rf.a14a36104d29927ab54f862a9837d584.jpg</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>19.5</v>
       </c>
       <c r="C15" t="n">
-        <v>20.4491</v>
+        <v>20.0849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1268,23 +1272,23 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>173.6437</v>
+        <v>145.2937</v>
       </c>
       <c r="P15" t="n">
-        <v>4.08982070757534</v>
+        <v>4.016987660166959</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>015_d2_jpg.rf.70e2f6dc9893c6e58cabccd7c011d5b9.jpg</t>
+          <t>015_d2_jpg.rf.dae752b5463a5088dc2770f784a243e6.jpg</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>19.5</v>
       </c>
       <c r="C16" t="n">
-        <v>22.8136</v>
+        <v>23.5567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1322,23 +1326,23 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>162.4594</v>
+        <v>130.975</v>
       </c>
       <c r="P16" t="n">
-        <v>4.562728287806062</v>
+        <v>4.711347967169307</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>016_d2_jpg.rf.65b8db683dc4f8cc8aaac8393cb41f39.jpg</t>
+          <t>016_d2_jpg.rf.d69ea271fc8ead7e00a19c4bff62665c.jpg</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>18.5</v>
       </c>
       <c r="C17" t="n">
-        <v>21.3113</v>
+        <v>21.4498</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1376,23 +1380,23 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>318.1758</v>
+        <v>263.4719</v>
       </c>
       <c r="P17" t="n">
-        <v>4.262252817467576</v>
+        <v>4.289962610813525</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>017_d0_jpg.rf.708a61dec88abfd33e593ec334f78b1d.jpg</t>
+          <t>017_d0_jpg.rf.e371f94baddb2eaf7462ec73ce042fb3.jpg</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>23.75</v>
       </c>
       <c r="C18" t="n">
-        <v>26.0532</v>
+        <v>26.2647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1416,7 +1420,11 @@
       <c r="I18" t="n">
         <v>1880</v>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
       <c r="K18" t="n">
         <v>11</v>
       </c>
@@ -1430,23 +1438,23 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>581.625</v>
+        <v>470</v>
       </c>
       <c r="P18" t="n">
-        <v>3.06508437567161</v>
+        <v>3.089967234042553</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>018_d1_jpg.rf.5bf79ee3a41faec6e55dc417b91586fc.jpg</t>
+          <t>018_d1_jpg.rf.4cb760e4db18ad5514645a6d9ee54a47.jpg</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>22.25</v>
       </c>
       <c r="C19" t="n">
-        <v>21.1078</v>
+        <v>20.7934</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1484,23 +1492,23 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>250.275</v>
+        <v>209.0062</v>
       </c>
       <c r="P19" t="n">
-        <v>3.247349515532914</v>
+        <v>3.198987876914656</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>019_d1_jpg.rf.3db79a352ad46867b221abf127fe08f8.jpg</t>
+          <t>019_d1_jpg.rf.b5bbd4289ae38c62eccbabb5ba23cee6.jpg</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>25.5</v>
       </c>
       <c r="C20" t="n">
-        <v>27.2827</v>
+        <v>27.6171</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1524,7 +1532,11 @@
       <c r="I20" t="n">
         <v>966</v>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
       <c r="K20" t="n">
         <v>11</v>
       </c>
@@ -1538,23 +1550,23 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>283.7625</v>
+        <v>230.9344</v>
       </c>
       <c r="P20" t="n">
-        <v>3.209724681732082</v>
+        <v>3.249073329915335</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>020_d0_jpg.rf.3e4b934f23cd8b513cc009cdb9d82b17.jpg</t>
+          <t>020_d0_jpg.rf.ac00bbc8dce23d8bb488146d95350cfe.jpg</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>22.5</v>
       </c>
       <c r="C21" t="n">
-        <v>21.9797</v>
+        <v>21.293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1578,7 +1590,11 @@
       <c r="I21" t="n">
         <v>450</v>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>牙形不夠細長</t>
+        </is>
+      </c>
       <c r="K21" t="n">
         <v>11</v>
       </c>
@@ -1592,23 +1608,23 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>161.0156</v>
+        <v>137.8125</v>
       </c>
       <c r="P21" t="n">
-        <v>2.585843235065422</v>
+        <v>2.505064489795918</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>021_d1_jpg.rf.9ae2277fadfdc6d0ff28f1441fdefe6c.jpg</t>
+          <t>021_d1_jpg.rf.ce2222b68f762d4951ed21a7e32abfa1.jpg</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>21.5</v>
       </c>
       <c r="C22" t="n">
-        <v>19.4874</v>
+        <v>20.5303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1646,23 +1662,23 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>251.175</v>
+        <v>197</v>
       </c>
       <c r="P22" t="n">
-        <v>2.998063899671543</v>
+        <v>3.158509137055838</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>022_d1_jpg.rf.65006c8cf3a5a9b18f602e9ac24a4d85.jpg</t>
+          <t>022_d1_jpg.rf.f1be5fe64a13290e324eac2bae09a30c.jpg</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>25.1033</v>
+        <v>24.7551</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1700,23 +1716,23 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>283.4563</v>
+        <v>230.5625</v>
       </c>
       <c r="P23" t="n">
-        <v>2.953326491596765</v>
+        <v>2.912364760097587</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>023_d1_jpg.rf.a0f1e12c783fc45b2c71606440cd9cdf.jpg</t>
+          <t>023_d1_jpg.rf.19149aa200ed2ab6d2f9f95936683869.jpg</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>19.5</v>
       </c>
       <c r="C24" t="n">
-        <v>19.3604</v>
+        <v>19.3319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1758,23 +1774,23 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>311.1609</v>
+        <v>256.3203</v>
       </c>
       <c r="P24" t="n">
-        <v>2.27769138089008</v>
+        <v>2.274342297508235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>024_d2_jpg.rf.e037af81f2e84ee3621c491021bbedca.jpg</t>
+          <t>024_d2_jpg.rf.dfde607ee1a1abd88070f4a4e9c873a7.jpg</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>18.5</v>
       </c>
       <c r="C25" t="n">
-        <v>17.4438</v>
+        <v>17.2502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1798,7 +1814,11 @@
       <c r="I25" t="n">
         <v>745</v>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>牙形不夠細長</t>
+        </is>
+      </c>
       <c r="K25" t="n">
         <v>22</v>
       </c>
@@ -1812,23 +1832,23 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>259.5859</v>
+        <v>217.6797</v>
       </c>
       <c r="P25" t="n">
-        <v>2.6836669480122</v>
+        <v>2.653877233384647</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>026_d1_jpg.rf.72f8bbf079abb3c27d2d96190ecb7b7c.jpg</t>
+          <t>026_d1_jpg.rf.cbebc4e773617f19901fea82d27a7481.jpg</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>21.25</v>
       </c>
       <c r="C26" t="n">
-        <v>22.2139</v>
+        <v>22.1125</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1870,23 +1890,23 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>318.1906</v>
+        <v>264.9313</v>
       </c>
       <c r="P26" t="n">
-        <v>2.613396184551021</v>
+        <v>2.601467625758074</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>027_d0_jpg.rf.069f8c640691d4f7444bb89af4656ea7.jpg</t>
+          <t>027_d0_jpg.rf.172e9a9162be8b33b29886a7a7c2044f.jpg</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>19.25</v>
       </c>
       <c r="C27" t="n">
-        <v>24.622</v>
+        <v>23.7957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1928,23 +1948,23 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>261.875</v>
+        <v>229.1406</v>
       </c>
       <c r="P27" t="n">
-        <v>2.896700715990453</v>
+        <v>2.799498212014806</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>028_d1_jpg.rf.f57ec19622124ac1188f2ba3ec1abeaf.jpg</t>
+          <t>028_d1_jpg.rf.c32bbe4c003dc55f0e7db7b213e120d5.jpg</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>21.75</v>
       </c>
       <c r="C28" t="n">
-        <v>24.7725</v>
+        <v>24.6952</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1982,23 +2002,23 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>291.9156</v>
+        <v>235.675</v>
       </c>
       <c r="P28" t="n">
-        <v>2.914407109452184</v>
+        <v>2.905323008380184</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>029_d1_jpg.rf.bb10ad14fba1241f3e45fd6287010555.jpg</t>
+          <t>029_d1_jpg.rf.60d86604165d1ad5ec3e55f3d4a92ed0.jpg</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>20.75</v>
       </c>
       <c r="C29" t="n">
-        <v>23.1961</v>
+        <v>23.4211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2036,23 +2056,23 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>157.0641</v>
+        <v>128.3766</v>
       </c>
       <c r="P29" t="n">
-        <v>2.728948244697547</v>
+        <v>2.755418822433372</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>030_d1_jpg.rf.5ebd911c8c14b6d894d03468ab54db54.jpg</t>
+          <t>030_d1_jpg.rf.642032a0ccf11c21478fc98e431d62c2.jpg</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>21.5</v>
       </c>
       <c r="C30" t="n">
-        <v>23.3282</v>
+        <v>22.5869</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2090,23 +2110,23 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>304.2188</v>
+        <v>257.2031</v>
       </c>
       <c r="P30" t="n">
-        <v>2.744498696333034</v>
+        <v>2.657287567684837</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>031_d1_jpg.rf.027a2168cae2921b8f520ac35b5091c7.jpg</t>
+          <t>031_d1_jpg.rf.0a64e6a881d6244f0916844a19eec968.jpg</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>19.5</v>
       </c>
       <c r="C31" t="n">
-        <v>24.2721</v>
+        <v>24.1736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2130,7 +2150,11 @@
       <c r="I31" t="n">
         <v>1706</v>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
       <c r="K31" t="n">
         <v>21</v>
       </c>
@@ -2144,23 +2168,23 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>573.1094000000001</v>
+        <v>477.1469</v>
       </c>
       <c r="P31" t="n">
-        <v>2.855541018870044</v>
+        <v>2.843954765293456</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>032_d0_jpg.rf.24d3028acaa9d78ef4b6a5190aa6dd17.jpg</t>
+          <t>032_d0_jpg.rf.9285b7976f1da306fcfec57b8ac03392.jpg</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>19.5</v>
       </c>
       <c r="C32" t="n">
-        <v>25.0053</v>
+        <v>25.0694</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2198,23 +2222,23 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>549.6094000000001</v>
+        <v>444.9219</v>
       </c>
       <c r="P32" t="n">
-        <v>2.941800485945109</v>
+        <v>2.949338749115294</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>034_d1_jpg.rf.75b8f74e83d0a432cafb48b71b900e7f.jpg</t>
+          <t>034_d1_jpg.rf.c71a61069d50d94065010b64a9ffd1a5.jpg</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>21</v>
       </c>
       <c r="C33" t="n">
-        <v>23.4222</v>
+        <v>23.6628</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2252,23 +2276,23 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>452.35</v>
+        <v>373.325</v>
       </c>
       <c r="P33" t="n">
-        <v>3.6034174864596</v>
+        <v>3.640426705953258</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>036_d0_jpg.rf.5f87f7a84eec81ff2996ded4e3ab17c5.jpg</t>
+          <t>036_d0_jpg.rf.cd77e3ba407312ef40811e53f8234dfc.jpg</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>20.25</v>
       </c>
       <c r="C34" t="n">
-        <v>23.3428</v>
+        <v>23.0528</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2310,23 +2334,23 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>202.8313</v>
+        <v>172.2844</v>
       </c>
       <c r="P34" t="n">
-        <v>3.591201653788148</v>
+        <v>3.5465828595044</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>037_d0_jpg.rf.7ca9e76521533829c44da4a608e38227.jpg</t>
+          <t>037_d0_jpg.rf.26d3c419d8aa463d4ccb6f397ffd8a0d.jpg</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>21.5</v>
       </c>
       <c r="C35" t="n">
-        <v>22.7577</v>
+        <v>22.5655</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2364,23 +2388,23 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>278.4016</v>
+        <v>234.7063</v>
       </c>
       <c r="P35" t="n">
-        <v>2.677379727702715</v>
+        <v>2.654770238378774</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>038_d1_jpg.rf.105efb541fd013d353eeea0415e0ad08.jpg</t>
+          <t>038_d1_jpg.rf.b3c9c20efafeb14a18e816c6ca8d7855.jpg</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>19.5</v>
       </c>
       <c r="C36" t="n">
-        <v>20.4996</v>
+        <v>19.3122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2418,23 +2442,23 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>239.7656</v>
+        <v>198.5938</v>
       </c>
       <c r="P36" t="n">
-        <v>3.153781026135525</v>
+        <v>2.971112894763079</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>039_d1_jpg.rf.9325f3f6007c15ce956824ba4ed19434.jpg</t>
+          <t>039_d1_jpg.rf.d49148703ce141d56d8246b6549a4760.jpg</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>25</v>
       </c>
       <c r="C37" t="n">
-        <v>26.3232</v>
+        <v>25.6194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2476,23 +2500,23 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>294.4781</v>
+        <v>240.5391</v>
       </c>
       <c r="P37" t="n">
-        <v>3.096842176039576</v>
+        <v>3.014047196484896</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>040_d0_jpg.rf.bfd5d4db30aed99753ef178ebd96f211.jpg</t>
+          <t>040_d0_jpg.rf.8f2cbb2d727d030158755add43241d12.jpg</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>19</v>
       </c>
       <c r="C38" t="n">
-        <v>22.2286</v>
+        <v>19.7364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2518,7 +2542,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>冠寬位置異常</t>
+          <t>牙形不夠細長</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2534,23 +2558,23 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>276.8063</v>
+        <v>258.5953</v>
       </c>
       <c r="P38" t="n">
-        <v>2.615124366750323</v>
+        <v>2.321933151917301</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>041_d1_jpg.rf.6d42d568e5349b1bc1401afb1a032541.jpg</t>
+          <t>041_d1_jpg.rf.cb07a3b2089be3295cec77cb809df396.jpg</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>19</v>
       </c>
       <c r="C39" t="n">
-        <v>23.9062</v>
+        <v>24.3924</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2592,23 +2616,23 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>298.3125</v>
+        <v>241.425</v>
       </c>
       <c r="P39" t="n">
-        <v>2.81249126335638</v>
+        <v>2.869689965827896</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>042_d2_jpg.rf.d4047f8c04a5c6faf623949469d955f6.jpg</t>
+          <t>042_d2_jpg.rf.b762e168ff32523cefa4b66b23ff4fa2.jpg</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>21</v>
       </c>
       <c r="C40" t="n">
-        <v>24.6687</v>
+        <v>25.5134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2646,23 +2670,23 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>378.4656</v>
+        <v>304.1656</v>
       </c>
       <c r="P40" t="n">
-        <v>3.795184555742979</v>
+        <v>3.92513124429587</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>043_d1_jpg.rf.4f546939d5c894ee236287322e2a2e78.jpg</t>
+          <t>043_d1_jpg.rf.ff8a6dfd8d13cd19c47af53d9384c375.jpg</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>20.5</v>
       </c>
       <c r="C41" t="n">
-        <v>20.2024</v>
+        <v>20.2021</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2700,23 +2724,23 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>264.2937</v>
+        <v>214.4016</v>
       </c>
       <c r="P41" t="n">
-        <v>3.108066518422497</v>
+        <v>3.108014119297617</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>044_d2_jpg.rf.0b53fdb22fc286dd9e8a4b21f2d31d85.jpg</t>
+          <t>044_d2_jpg.rf.da81051630fbd29d52f53bff91f9d894.jpg</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>19.25</v>
       </c>
       <c r="C42" t="n">
-        <v>18.5376</v>
+        <v>18.9867</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2758,23 +2782,23 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>112.5719</v>
+        <v>89.7812</v>
       </c>
       <c r="P42" t="n">
-        <v>3.707512265494319</v>
+        <v>3.797336190650158</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>045_d3_jpg.rf.b35aec29b73f7b5084e0cc6459be15f9.jpg</t>
+          <t>045_d3_jpg.rf.e7b47a708da0d4954eb6d698fb50fbc2.jpg</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>20</v>
       </c>
       <c r="C43" t="n">
-        <v>20.0071</v>
+        <v>19.4251</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2812,23 +2836,23 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>198.3125</v>
+        <v>165.0625</v>
       </c>
       <c r="P43" t="n">
-        <v>3.637656224393318</v>
+        <v>3.531837940174177</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>046_d1_jpg.rf.f55bcf163d5589c797bef5d8b412f9c1.jpg</t>
+          <t>046_d1_jpg.rf.ec359b9c3be4b77858006f1894a4fe89.jpg</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>20</v>
       </c>
       <c r="C44" t="n">
-        <v>21.4388</v>
+        <v>21.1873</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2852,11 +2876,7 @@
       <c r="I44" t="n">
         <v>841</v>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>冠寬位置異常</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
         <v>41</v>
       </c>
@@ -2870,23 +2890,23 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>183.9688</v>
+        <v>155.0594</v>
       </c>
       <c r="P44" t="n">
-        <v>4.287769447862899</v>
+        <v>4.237458032212171</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>047_d0_jpg.rf.9b7b50de4731edce3e8002cfad34afd5.jpg</t>
+          <t>047_d0_jpg.rf.7cdd34b48873ec944be1cf54e2bbe7de.jpg</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>20</v>
       </c>
       <c r="C45" t="n">
-        <v>18.7562</v>
+        <v>18.6451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2928,23 +2948,23 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>316.1562</v>
+        <v>266.6094</v>
       </c>
       <c r="P45" t="n">
-        <v>2.206611162457039</v>
+        <v>2.193542688292311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>048_d0_jpg.rf.9207ac2109faa2bec8a4d9eb813c70d6.jpg</t>
+          <t>048_d0_jpg.rf.b9d97351b8bbb80a941065b51ab298c2.jpg</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>22</v>
       </c>
       <c r="C46" t="n">
-        <v>22.8708</v>
+        <v>22.3256</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2982,23 +3002,23 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>660.2030999999999</v>
+        <v>554.8516</v>
       </c>
       <c r="P46" t="n">
-        <v>2.690680792016881</v>
+        <v>2.62653942063067</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>049_d0_jpg.rf.6310b61e8ff6675b1a465351852f5a51.jpg</t>
+          <t>049_d0_jpg.rf.a92e6c133f098bc8b880cd0c95917303.jpg</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>22</v>
       </c>
       <c r="C47" t="n">
-        <v>22.6799</v>
+        <v>21.8486</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3036,23 +3056,23 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>640.4844000000001</v>
+        <v>542.5938</v>
       </c>
       <c r="P47" t="n">
-        <v>2.668229390130345</v>
+        <v>2.570423583903834</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>050_d1_jpg.rf.84fdb6257046bd80c5e84db13b1750bf.jpg</t>
+          <t>050_d1_jpg.rf.84fe073fb9b1dc338920f1a858bf5e87.jpg</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>23</v>
       </c>
       <c r="C48" t="n">
-        <v>20.4474</v>
+        <v>21.6512</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3090,23 +3110,23 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>508.2141</v>
+        <v>418.3641</v>
       </c>
       <c r="P48" t="n">
-        <v>3.145753925363346</v>
+        <v>3.330955261218637</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>051_d0_jpg.rf.cafc462d1790b6c6ca401c3e8b037955.jpg</t>
+          <t>051_d0_jpg.rf.37687ccc93b1c959bc854c565f03d537.jpg</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>21.75</v>
       </c>
       <c r="C49" t="n">
-        <v>23.1502</v>
+        <v>23.1213</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3144,23 +3164,23 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>599.9578</v>
+        <v>488.5563</v>
       </c>
       <c r="P49" t="n">
-        <v>2.723551889816251</v>
+        <v>2.720147503982653</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>052_d1_jpg.rf.7418283c5166896604237ccbcf8dc037.jpg</t>
+          <t>052_d1_jpg.rf.3b6940e484968d5a668f3c1f9ae214aa.jpg</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>21.5</v>
       </c>
       <c r="C50" t="n">
-        <v>23.3709</v>
+        <v>23.5712</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3198,23 +3218,23 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>592.6686999999999</v>
+        <v>495.2437</v>
       </c>
       <c r="P50" t="n">
-        <v>2.74951975699071</v>
+        <v>2.773085048835553</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>054_d3_jpg.rf.2821b14c46e7909ff2bdbba385d59b6f.jpg</t>
+          <t>054_d3_jpg.rf.873773ad3ada175d0933d8f47c5af6c8.jpg</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>19.2</v>
       </c>
       <c r="C51" t="n">
-        <v>18.6058</v>
+        <v>18.2844</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3238,11 +3258,7 @@
       <c r="I51" t="n">
         <v>1603</v>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>冠寬位置異常</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
         <v>32</v>
       </c>
@@ -3256,23 +3272,23 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>438.3203</v>
+        <v>370.6938</v>
       </c>
       <c r="P51" t="n">
-        <v>3.382879369264896</v>
+        <v>3.324434344464353</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>055_d2_jpg.rf.7d9db9b7ce9613b3c0bfdf073bd012b3.jpg</t>
+          <t>055_d2_jpg.rf.165029284ddb2793ad8deac65e1c3f91.jpg</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>17.5</v>
       </c>
       <c r="C52" t="n">
-        <v>18.1998</v>
+        <v>17.9066</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3314,23 +3330,23 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>391.0766</v>
+        <v>321.6547</v>
       </c>
       <c r="P52" t="n">
-        <v>3.639950843389761</v>
+        <v>3.581314372213433</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>056_d1_jpg.rf.379c6c5dbc15404b789258691866c2b0.jpg</t>
+          <t>056_d1_jpg.rf.9429abcc45818b6e31b5dd0c7d043dfd.jpg</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>18.4</v>
       </c>
       <c r="C53" t="n">
-        <v>18.6765</v>
+        <v>18.609</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3354,7 +3370,11 @@
       <c r="I53" t="n">
         <v>1536</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
       <c r="K53" t="n">
         <v>41</v>
       </c>
@@ -3368,23 +3388,23 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>379.2</v>
+        <v>316.8</v>
       </c>
       <c r="P53" t="n">
-        <v>3.735303533755275</v>
+        <v>3.721802398989899</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>057_d2_jpg.rf.e31cea9a4d92a78adb15f39ce5d86ba8.jpg</t>
+          <t>057_d2_jpg.rf.cdb9bd6640c5fb65eee49172b52cbf93.jpg</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>19</v>
       </c>
       <c r="C54" t="n">
-        <v>16.0789</v>
+        <v>16.0005</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3408,7 +3428,11 @@
       <c r="I54" t="n">
         <v>1459</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
       <c r="K54" t="n">
         <v>42</v>
       </c>
@@ -3426,23 +3450,23 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>471.8953</v>
+        <v>387.5469</v>
       </c>
       <c r="P54" t="n">
-        <v>2.923445306617802</v>
+        <v>2.909190603769505</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>058_d0_jpg.rf.ae804795ef69cfb93e94e1fdf33195a7.jpg</t>
+          <t>058_d0_jpg.rf.ab8df462eb38a7cfd65cff39b2992cdb.jpg</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>19.5</v>
       </c>
       <c r="C55" t="n">
-        <v>23.4575</v>
+        <v>21.271</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3466,7 +3490,11 @@
       <c r="I55" t="n">
         <v>780</v>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>牙形不夠細長</t>
+        </is>
+      </c>
       <c r="K55" t="n">
         <v>11</v>
       </c>
@@ -3480,23 +3508,23 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>264.4688</v>
+        <v>240.0938</v>
       </c>
       <c r="P55" t="n">
-        <v>2.759701711506235</v>
+        <v>2.502471117538229</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>059_d1_jpg.rf.7518cf6b72f813a6057c1bb9e8b0ea4f.jpg</t>
+          <t>059_d1_jpg.rf.3f42e0602c43c121b117dcecca57b59d.jpg</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>20.5</v>
       </c>
       <c r="C56" t="n">
-        <v>24.2159</v>
+        <v>22.2482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3520,7 +3548,11 @@
       <c r="I56" t="n">
         <v>864</v>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>牙形不夠細長、牙位與寬度法方向不一致</t>
+        </is>
+      </c>
       <c r="K56" t="n">
         <v>21</v>
       </c>
@@ -3534,23 +3566,23 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>292.95</v>
+        <v>278.1</v>
       </c>
       <c r="P56" t="n">
-        <v>2.848927462024236</v>
+        <v>2.617431499460626</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>060_jpg.rf.26630a77bf453ed3cdc227f0f3fcf9d0.jpg</t>
+          <t>060_jpg.rf.4a64dc5e1c74ac81bc312481b7e581e5.jpg</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>21</v>
       </c>
       <c r="C57" t="n">
-        <v>18.6041</v>
+        <v>18.5556</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3566,13 +3598,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.321875</v>
+        <v>1.3390625</v>
       </c>
       <c r="H57" t="n">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I57" t="n">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3592,23 +3624,23 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>214.1437</v>
+        <v>174.0781</v>
       </c>
       <c r="P57" t="n">
-        <v>3.720825314963737</v>
+        <v>3.711120468341509</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>061_d1_jpg.rf.d829f21952ac35c555d13a51f5a580a2.jpg</t>
+          <t>061_d1_jpg.rf.db8df0c1f429b3e2e71267f1fbffc989.jpg</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>23.5</v>
       </c>
       <c r="C58" t="n">
-        <v>24.8642</v>
+        <v>24.5019</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3646,23 +3678,23 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>349.0594</v>
+        <v>297.3469</v>
       </c>
       <c r="P58" t="n">
-        <v>3.825265556521325</v>
+        <v>3.769519036519298</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>062_d0_jpg.rf.ded7d8972acae712489fcab7f698f5ae.jpg</t>
+          <t>062_d0_jpg.rf.420ca201dfb51cbc2be18110aeb5765e.jpg</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>20.5</v>
       </c>
       <c r="C59" t="n">
-        <v>24.6</v>
+        <v>24.0683</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3700,23 +3732,23 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>287.2266</v>
+        <v>235.125</v>
       </c>
       <c r="P59" t="n">
-        <v>2.894114611947501</v>
+        <v>2.831568314726209</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>063_d1_jpg.rf.da08e84fee24b5569efa2a750d1bff2f.jpg</t>
+          <t>063_d1_jpg.rf.3d9a28c55c36d0806810a87e5ea9470f.jpg</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>21.5</v>
       </c>
       <c r="C60" t="n">
-        <v>23.4755</v>
+        <v>25.2834</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -3754,23 +3786,23 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>283.8281</v>
+        <v>233.8203</v>
       </c>
       <c r="P60" t="n">
-        <v>2.761819213812867</v>
+        <v>2.974515044245516</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>064_d2_jpg.rf.c8e62f1580424dee4c21d34d668a4e64.jpg</t>
+          <t>064_d2_jpg.rf.7b174bc08e6f9220d59234147d56740a.jpg</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>20</v>
       </c>
       <c r="C61" t="n">
-        <v>23.9232</v>
+        <v>23.3972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -3808,23 +3840,23 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>214.225</v>
+        <v>177.65</v>
       </c>
       <c r="P61" t="n">
-        <v>3.680490138872681</v>
+        <v>3.599568252181255</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>065_d0_jpg.rf.959e6c5e9deaf114048e57d62b769ac0.jpg</t>
+          <t>065_d0_jpg.rf.ee2a42597e7bd3f73156286c58ff062a.jpg</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>23</v>
       </c>
       <c r="C62" t="n">
-        <v>22.5428</v>
+        <v>23.1667</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -3862,23 +3894,23 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>315.0125</v>
+        <v>256.6266</v>
       </c>
       <c r="P62" t="n">
-        <v>2.652091583667315</v>
+        <v>2.72549377188491</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>066_d1_jpg.rf.c23dcc0077b0cdf367a6f29daa31affc.jpg</t>
+          <t>066_d1_jpg.rf.cca8412d959b332e5836a79cb1f63bb9.jpg</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>21.5</v>
       </c>
       <c r="C63" t="n">
-        <v>20.8442</v>
+        <v>20.4568</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -3916,23 +3948,23 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>256.7375</v>
+        <v>217.1344</v>
       </c>
       <c r="P63" t="n">
-        <v>3.206793320025317</v>
+        <v>3.147203298970591</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>067_d0_jpg.rf.ac90bce7f88c1b868e5f95777451272a.jpg</t>
+          <t>067_d0_jpg.rf.5e98d5946a7670ae9374f063be3378c8.jpg</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>22.5</v>
       </c>
       <c r="C64" t="n">
-        <v>24.7553</v>
+        <v>24.4345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -3970,23 +4002,23 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>176.5969</v>
+        <v>146.7375</v>
       </c>
       <c r="P64" t="n">
-        <v>2.912388043051719</v>
+        <v>2.874648266462219</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>068_d1_jpg.rf.4c942bc2ee8c89e7542268bf3b006b03.jpg</t>
+          <t>068_d1_jpg.rf.dccd7a7a1610957846e542d412bd78a8.jpg</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>19.25</v>
       </c>
       <c r="C65" t="n">
-        <v>22.8454</v>
+        <v>23.5804</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4010,7 +4042,11 @@
       <c r="I65" t="n">
         <v>750</v>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>冠寬位置異常</t>
+        </is>
+      </c>
       <c r="K65" t="n">
         <v>21</v>
       </c>
@@ -4024,23 +4060,23 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>267.1875</v>
+        <v>214.4531</v>
       </c>
       <c r="P65" t="n">
-        <v>2.687692350877193</v>
+        <v>2.774165073855309</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>069_d0_jpg.rf.52b762e91c73d1d37d7ff85ef3bab696.jpg</t>
+          <t>069_d0_jpg.rf.e7743bd9b6bf261cd082bb4e0ea61007.jpg</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>23.5</v>
       </c>
       <c r="C66" t="n">
-        <v>32.5541</v>
+        <v>30.2531</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -4078,23 +4114,23 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>231.3937</v>
+        <v>189.0656</v>
       </c>
       <c r="P66" t="n">
-        <v>3.829894245176078</v>
+        <v>3.559185277490987</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>070_d1_jpg.rf.1c5eda7e45ce43492d0c6f1cdfbd0d5c.jpg</t>
+          <t>070_d1_jpg.rf.dc10b95de92898fa67c004505cf51be2.jpg</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>21.5</v>
       </c>
       <c r="C67" t="n">
-        <v>18.6993</v>
+        <v>18.9732</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4132,23 +4168,23 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>267.15</v>
+        <v>218.3438</v>
       </c>
       <c r="P67" t="n">
-        <v>2.876811154781958</v>
+        <v>2.918950755643165</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>071_d2_jpg.rf.56b09cdbf1c783b3b1e6f5b2bc96d8b4.jpg</t>
+          <t>071_d2_jpg.rf.0959cd07ae695e4405ee3ab991b172da.jpg</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>19</v>
       </c>
       <c r="C68" t="n">
-        <v>19.0382</v>
+        <v>19.011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4190,10 +4226,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>282.2695</v>
+        <v>231.1922</v>
       </c>
       <c r="P68" t="n">
-        <v>3.807642696075914</v>
+        <v>3.802195748818515</v>
       </c>
     </row>
   </sheetData>
